--- a/data/trans_dic/P2C_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Entrevistados que realiza cuidados a personas del hogar que lo requieren</t>
+          <t>Entrevistados que realiza cuidados a personas del hogar que lo requieren (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>51,96; 73,24</t>
+          <t>51,35; 72,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>76,88; 93,21</t>
+          <t>76,99; 92,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64,87; 86,22</t>
+          <t>65,17; 85,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,85; 56,95</t>
+          <t>24,25; 58,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,19; 74,75</t>
+          <t>52,81; 74,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,9; 92,7</t>
+          <t>78,15; 92,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,78; 83,59</t>
+          <t>65,12; 83,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,84; 50,75</t>
+          <t>29,4; 51,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>55,22; 70,58</t>
+          <t>56,19; 70,24</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80,25; 91,28</t>
+          <t>80,46; 90,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68,3; 82,37</t>
+          <t>68,71; 83,08</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,16; 50,22</t>
+          <t>30,26; 49,86</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>62,96; 71,34</t>
+          <t>62,91; 71,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86,01; 91,93</t>
+          <t>86,02; 91,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68,57; 76,26</t>
+          <t>68,49; 76,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,62; 35,15</t>
+          <t>24,73; 35,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>64,23; 72,11</t>
+          <t>64,5; 72,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,57; 88,59</t>
+          <t>82,55; 88,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,8; 76,76</t>
+          <t>69,19; 76,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,14; 40,35</t>
+          <t>31,16; 40,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>64,69; 70,56</t>
+          <t>65,1; 70,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84,85; 89,32</t>
+          <t>85,03; 89,42</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69,71; 75,2</t>
+          <t>69,91; 75,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,64; 36,67</t>
+          <t>29,47; 36,41</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72,05; 83,45</t>
+          <t>71,88; 83,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89,09; 96,61</t>
+          <t>89,05; 96,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67,14; 79,79</t>
+          <t>66,15; 79,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,52; 29,14</t>
+          <t>18,05; 29,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>66,03; 78,06</t>
+          <t>65,28; 78,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>89,33; 96,45</t>
+          <t>89,57; 96,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,6; 87,3</t>
+          <t>77,07; 87,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,54; 30,09</t>
+          <t>18,21; 30,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>70,9; 79,48</t>
+          <t>70,39; 79,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>90,68; 95,79</t>
+          <t>90,84; 95,89</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73,8; 81,94</t>
+          <t>73,85; 81,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,68; 28,01</t>
+          <t>19,78; 28,13</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>66,16; 72,69</t>
+          <t>66,23; 72,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87,35; 91,87</t>
+          <t>87,45; 92,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69,78; 76,16</t>
+          <t>69,63; 76,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,3; 33,42</t>
+          <t>25,34; 33,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>65,3; 71,81</t>
+          <t>65,58; 72,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,42; 89,91</t>
+          <t>85,3; 90,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,78; 78,78</t>
+          <t>72,74; 78,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,57; 36,88</t>
+          <t>29,85; 36,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>67,07; 71,51</t>
+          <t>67,03; 71,83</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>87,28; 90,51</t>
+          <t>87,12; 90,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72,2; 76,7</t>
+          <t>72,33; 76,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,96; 34,04</t>
+          <t>28,91; 34,57</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Entrevistados que realiza cuidados a personas del hogar que lo requieren (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>35212</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>47890</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>31130</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20399</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>32945</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>53810</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>38672</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>24782</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>68157</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>101700</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>69802</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>45181</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>28991; 40653</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42715; 51507</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>26487; 34878</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13259; 31848</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>27128; 38100</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>48521; 57372</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>33365; 42841</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>18228; 31915</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>60592; 75746</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>94601; 106909</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>63127; 76334</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>35307; 58177</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>811</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>208759</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>271554</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>252940</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>142281</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>241812</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>291627</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>277379</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>181850</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>450570</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>563181</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>530319</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>324131</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>195215; 221347</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>262076; 279418</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>238826; 265469</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>113880; 162185</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>228108; 256178</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>280504; 301202</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>262815; 291306</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>160975; 210915</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>432263; 467828</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>547981; 576275</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>509365; 549977</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>287961; 355726</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>106760</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>109494</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>99573</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>35113</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89064</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>128208</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>115798</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>44413</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>195824</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>237703</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>215371</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>79526</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>98178; 113720</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>104039; 112860</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>89985; 108045</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>26997; 44201</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>80648; 96860</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>122619; 132186</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>107850; 122609</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>33388; 55167</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>183100; 205643</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>230471; 243303</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>203796; 225769</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>65845; 93661</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1292</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>1221</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>350731</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>428939</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>383642</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>197792</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>363821</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>473645</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>431850</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>251045</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>714551</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>902584</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>815492</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>448837</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>333400; 366650</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>417091; 439171</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>365828; 399645</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>168438; 220403</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>346609; 381488</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>459598; 485395</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>415346; 448830</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>227448; 279996</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>691673; 741191</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>884960; 917749</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>792992; 837837</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>412526; 493161</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2C_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>51,35; 72,0</t>
+          <t>51,93; 72,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>76,99; 92,83</t>
+          <t>77,03; 92,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65,17; 85,82</t>
+          <t>64,23; 85,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,25; 58,25</t>
+          <t>23,62; 58,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,81; 74,17</t>
+          <t>54,11; 74,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,15; 92,4</t>
+          <t>78,67; 92,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,12; 83,61</t>
+          <t>64,18; 84,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,4; 51,47</t>
+          <t>30,52; 51,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>56,19; 70,24</t>
+          <t>55,18; 70,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80,46; 90,93</t>
+          <t>80,73; 91,53</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68,71; 83,08</t>
+          <t>67,77; 82,79</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,26; 49,86</t>
+          <t>29,93; 50,04</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>62,91; 71,33</t>
+          <t>62,86; 71,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86,02; 91,72</t>
+          <t>86,23; 91,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68,49; 76,13</t>
+          <t>68,64; 76,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,73; 35,22</t>
+          <t>25,29; 34,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>64,5; 72,44</t>
+          <t>64,35; 72,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,55; 88,64</t>
+          <t>82,49; 88,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,19; 76,69</t>
+          <t>69,35; 77,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,16; 40,83</t>
+          <t>30,8; 40,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65,1; 70,46</t>
+          <t>65,15; 70,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85,03; 89,42</t>
+          <t>85,37; 89,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69,91; 75,49</t>
+          <t>70,07; 75,54</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,47; 36,41</t>
+          <t>29,39; 36,34</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>71,88; 83,26</t>
+          <t>71,93; 83,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89,05; 96,6</t>
+          <t>89,58; 96,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,15; 79,43</t>
+          <t>66,54; 78,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,05; 29,56</t>
+          <t>17,79; 29,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>65,28; 78,4</t>
+          <t>65,14; 78,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>89,57; 96,56</t>
+          <t>89,89; 96,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>77,07; 87,62</t>
+          <t>76,68; 87,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,21; 30,09</t>
+          <t>18,85; 30,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>70,39; 79,06</t>
+          <t>70,54; 79,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>90,84; 95,89</t>
+          <t>91,01; 95,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73,85; 81,81</t>
+          <t>73,34; 81,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,78; 28,13</t>
+          <t>19,88; 28,61</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>66,23; 72,84</t>
+          <t>66,48; 72,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87,45; 92,08</t>
+          <t>87,71; 91,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69,63; 76,07</t>
+          <t>69,96; 76,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,34; 33,16</t>
+          <t>25,37; 33,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>65,58; 72,18</t>
+          <t>65,6; 72,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,3; 90,09</t>
+          <t>85,66; 90,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,74; 78,6</t>
+          <t>72,45; 78,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,85; 36,75</t>
+          <t>29,46; 37,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>67,03; 71,83</t>
+          <t>66,82; 71,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>87,12; 90,35</t>
+          <t>87,09; 90,42</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72,33; 76,42</t>
+          <t>72,17; 76,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,91; 34,57</t>
+          <t>28,72; 33,95</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>28991; 40653</t>
+          <t>29319; 40755</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42715; 51507</t>
+          <t>42741; 51472</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26487; 34878</t>
+          <t>26105; 34829</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13259; 31848</t>
+          <t>12917; 31971</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27128; 38100</t>
+          <t>27796; 38119</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48521; 57372</t>
+          <t>48848; 57583</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33365; 42841</t>
+          <t>32882; 43438</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18228; 31915</t>
+          <t>18923; 31690</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60592; 75746</t>
+          <t>59499; 75975</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>94601; 106909</t>
+          <t>94912; 107615</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63127; 76334</t>
+          <t>62262; 76064</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35307; 58177</t>
+          <t>34924; 58390</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>195215; 221347</t>
+          <t>195061; 223139</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>262076; 279418</t>
+          <t>262695; 279880</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>238826; 265469</t>
+          <t>239346; 266136</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>113880; 162185</t>
+          <t>116463; 160830</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>228108; 256178</t>
+          <t>227569; 255192</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>280504; 301202</t>
+          <t>280295; 301359</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>262815; 291306</t>
+          <t>263455; 293577</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>160975; 210915</t>
+          <t>159115; 208033</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>432263; 467828</t>
+          <t>432589; 469943</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>547981; 576275</t>
+          <t>550182; 576720</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>509365; 549977</t>
+          <t>510497; 550379</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>287961; 355726</t>
+          <t>287197; 355078</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>98178; 113720</t>
+          <t>98249; 113989</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>104039; 112860</t>
+          <t>104652; 113071</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>89985; 108045</t>
+          <t>90510; 107382</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26997; 44201</t>
+          <t>26604; 43747</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>80648; 96860</t>
+          <t>80473; 97282</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>122619; 132186</t>
+          <t>123058; 131854</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>107850; 122609</t>
+          <t>107303; 122208</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33388; 55167</t>
+          <t>34566; 56522</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183100; 205643</t>
+          <t>183495; 206613</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>230471; 243303</t>
+          <t>230908; 243142</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>203796; 225769</t>
+          <t>202375; 225869</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>65845; 93661</t>
+          <t>66167; 95250</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>333400; 366650</t>
+          <t>334656; 367316</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>417091; 439171</t>
+          <t>418324; 438557</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>365828; 399645</t>
+          <t>367557; 401043</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>168438; 220403</t>
+          <t>168617; 221455</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>346609; 381488</t>
+          <t>346730; 380608</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>459598; 485395</t>
+          <t>461494; 486339</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>415346; 448830</t>
+          <t>413730; 448105</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>227448; 279996</t>
+          <t>224471; 283042</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>691673; 741191</t>
+          <t>689538; 738597</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>884960; 917749</t>
+          <t>884572; 918467</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>792992; 837837</t>
+          <t>791295; 838073</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>412526; 493161</t>
+          <t>409681; 484434</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>64,13%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>86,66%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>75,48%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>41,03%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>62,36%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>86,31%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>76,6%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>37,31%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>64,13%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>86,66%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>75,48%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,43%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>51,93; 72,18</t>
+          <t>52,19; 74,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>77,03; 92,77</t>
+          <t>78,9; 92,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64,23; 85,7</t>
+          <t>63,78; 83,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,62; 58,47</t>
+          <t>29,54; 51,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>54,11; 74,2</t>
+          <t>51,96; 73,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,67; 92,74</t>
+          <t>76,88; 93,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,18; 84,78</t>
+          <t>64,87; 86,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,52; 51,11</t>
+          <t>24,35; 47,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>55,18; 70,46</t>
+          <t>55,22; 70,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80,73; 91,53</t>
+          <t>80,25; 91,28</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67,77; 82,79</t>
+          <t>68,3; 82,37</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,93; 50,04</t>
+          <t>30,88; 47,6</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>68,38%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>85,82%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>73,02%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>36,09%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>67,27%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>89,14%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>72,53%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>30,9%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>68,38%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>85,82%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>73,02%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>34,75%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>62,86; 71,91</t>
+          <t>64,23; 72,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86,23; 91,87</t>
+          <t>82,57; 88,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68,64; 76,32</t>
+          <t>68,8; 76,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,29; 34,92</t>
+          <t>32,0; 40,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>64,35; 72,16</t>
+          <t>62,96; 71,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,49; 88,69</t>
+          <t>86,01; 91,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,35; 77,28</t>
+          <t>68,57; 76,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,8; 40,27</t>
+          <t>29,73; 37,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65,15; 70,78</t>
+          <t>64,69; 70,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85,37; 89,49</t>
+          <t>84,85; 89,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70,07; 75,54</t>
+          <t>69,71; 75,2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,39; 36,34</t>
+          <t>31,79; 38,02</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>72,09%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>93,65%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>82,75%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>25,18%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>78,17%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>93,72%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>73,2%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>23,48%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>72,09%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,65%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>82,75%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,19%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>71,93; 83,46</t>
+          <t>66,03; 78,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89,58; 96,78</t>
+          <t>89,33; 96,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,54; 78,94</t>
+          <t>76,6; 87,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,79; 29,25</t>
+          <t>19,31; 31,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>65,14; 78,74</t>
+          <t>72,05; 83,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>89,89; 96,32</t>
+          <t>89,09; 96,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,68; 87,34</t>
+          <t>67,14; 79,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,85; 30,83</t>
+          <t>16,99; 28,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>70,54; 79,43</t>
+          <t>70,9; 79,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91,01; 95,83</t>
+          <t>90,68; 95,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73,34; 81,85</t>
+          <t>73,8; 81,94</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,88; 28,61</t>
+          <t>19,94; 28,47</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>68,83%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>87,91%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>75,63%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33,87%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>69,68%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>89,93%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>73,02%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29,75%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>68,83%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>87,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>75,63%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>66,48; 72,97</t>
+          <t>65,3; 71,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87,71; 91,95</t>
+          <t>85,42; 89,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69,96; 76,33</t>
+          <t>72,78; 78,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,37; 33,31</t>
+          <t>30,61; 37,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>65,6; 72,01</t>
+          <t>66,16; 72,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,66; 90,27</t>
+          <t>87,35; 91,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,45; 78,47</t>
+          <t>69,78; 76,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,46; 37,15</t>
+          <t>27,79; 34,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>66,82; 71,58</t>
+          <t>67,07; 71,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>87,09; 90,42</t>
+          <t>87,28; 90,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72,17; 76,44</t>
+          <t>72,2; 76,7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,72; 33,95</t>
+          <t>30,36; 34,9</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>32945</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>53810</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>38672</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>23275</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>35212</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>47890</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>31130</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>20399</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>32945</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>53810</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>38672</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24782</t>
+          <t>16494</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45181</t>
+          <t>39769</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>29319; 40755</t>
+          <t>26809; 38402</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42741; 51472</t>
+          <t>48987; 57557</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26105; 34829</t>
+          <t>32678; 42831</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12917; 31971</t>
+          <t>16759; 29496</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27796; 38119</t>
+          <t>29340; 41350</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48848; 57583</t>
+          <t>42657; 51717</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32882; 43438</t>
+          <t>26364; 35041</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18923; 31690</t>
+          <t>11385; 22440</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>59499; 75975</t>
+          <t>59544; 76107</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>94912; 107615</t>
+          <t>94349; 107323</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62262; 76064</t>
+          <t>62749; 75682</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>34924; 58390</t>
+          <t>31962; 49257</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>313</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>393</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>389</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>213</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>241812</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>291627</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>277379</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>171682</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>208759</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>271554</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>252940</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>142281</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>241812</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>291627</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>277379</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>181850</t>
+          <t>143892</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>324131</t>
+          <t>315574</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>195061; 223139</t>
+          <t>227140; 255015</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>262695; 279880</t>
+          <t>280583; 301018</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>239346; 266136</t>
+          <t>261333; 291591</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>116463; 160830</t>
+          <t>152198; 194793</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>227569; 255192</t>
+          <t>195368; 221388</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>280295; 301359</t>
+          <t>262031; 280065</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>263455; 293577</t>
+          <t>239129; 265944</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>159115; 208033</t>
+          <t>128585; 160880</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>432589; 469943</t>
+          <t>429489; 468511</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>550182; 576720</t>
+          <t>546809; 575635</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>510497; 550379</t>
+          <t>507901; 547873</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>287197; 355078</t>
+          <t>288682; 345279</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>151</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>55</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>89064</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>128208</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>115798</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>42410</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>106760</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>109494</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>99573</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>35113</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>89064</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>128208</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>115798</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>44413</t>
+          <t>34595</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79526</t>
+          <t>77005</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>98249; 113989</t>
+          <t>81569; 96441</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>104652; 113071</t>
+          <t>122293; 132044</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>90510; 107382</t>
+          <t>107181; 122158</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26604; 43747</t>
+          <t>32526; 53004</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>80473; 97282</t>
+          <t>98405; 113973</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>123058; 131854</t>
+          <t>104076; 112868</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>107303; 122208</t>
+          <t>91326; 108533</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34566; 56522</t>
+          <t>25487; 42874</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183495; 206613</t>
+          <t>184433; 206742</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>230908; 243142</t>
+          <t>230082; 243034</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>202375; 225869</t>
+          <t>203643; 226107</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>66167; 95250</t>
+          <t>63488; 90645</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>520</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>617</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>589</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>295</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>363821</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>473645</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>431850</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>237366</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>350731</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>428939</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>383642</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>197792</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>363821</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>473645</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>431850</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>251045</t>
+          <t>194981</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>448837</t>
+          <t>432348</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>334656; 367316</t>
+          <t>345138; 379567</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>418324; 438557</t>
+          <t>460235; 484394</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>367557; 401043</t>
+          <t>415584; 449887</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>168617; 221455</t>
+          <t>214504; 264437</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>346730; 380608</t>
+          <t>333008; 365889</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>461494; 486339</t>
+          <t>416621; 438190</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>413730; 448105</t>
+          <t>366597; 400140</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>224471; 283042</t>
+          <t>174847; 216012</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>689538; 738597</t>
+          <t>692115; 737936</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>884572; 918467</t>
+          <t>886523; 919393</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>791295; 838073</t>
+          <t>791620; 840951</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>409681; 484434</t>
+          <t>403790; 464139</t>
         </is>
       </c>
     </row>
